--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:40:34+00:00</t>
+    <t>2026-06-16T09:03:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T09:03:15+00:00</t>
+    <t>2026-06-16T12:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:55:32+00:00</t>
+    <t>2026-06-16T13:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:06:44+00:00</t>
+    <t>2026-06-16T13:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:17:28+00:00</t>
+    <t>2026-06-16T13:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:23:35+00:00</t>
+    <t>2026-06-18T09:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:13:00+00:00</t>
+    <t>2026-06-22T13:30:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:30:33+00:00</t>
+    <t>2026-07-07T13:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:06:55+00:00</t>
+    <t>2026-09-02T03:42:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dem-ja-nein-ka-vs.xlsx
+++ b/ValueSet-dem-ja-nein-ka-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:42:42+00:00</t>
+    <t>2026-09-02T07:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
